--- a/Result/profitability/3550.xlsx
+++ b/Result/profitability/3550.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.10625</v>
+        <v>0.05749999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>14.36</v>
+        <v>15.55375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>-0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06250000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="N3" t="n">
-        <v>15.0125</v>
+        <v>15.875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1425</v>
+        <v>-0.04500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>14.5225</v>
+        <v>15.2425</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04625000000000001</v>
+        <v>0.03624999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>13.58375</v>
+        <v>13.855</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1175</v>
+        <v>0.1975</v>
       </c>
       <c r="N6" t="n">
-        <v>15.235</v>
+        <v>15.48375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1258,7 +1258,7 @@
         <v>1.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.27625</v>
+        <v>0.395</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1379,7 +1379,7 @@
         <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0.40875</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1502,7 +1502,7 @@
         <v>0.97</v>
       </c>
       <c r="M9" t="n">
-        <v>0.50375</v>
+        <v>0.5037499999999999</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
@@ -9677,6 +9677,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D74" t="n">
+        <v>992</v>
+      </c>
+      <c r="E74" t="n">
+        <v>218</v>
+      </c>
+      <c r="F74" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="G74" t="n">
+        <v>54</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>4.48%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>58</v>
+      </c>
+      <c r="K74" t="n">
+        <v>49</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-0.28625</v>
+      </c>
+      <c r="N74" t="n">
+        <v>14.32625</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.190476190476191</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0.620000000000001</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.03561171740379088</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>2.170000000000002</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.1368221941992436</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
